--- a/청파팀-엑셀.xlsx
+++ b/청파팀-엑셀.xlsx
@@ -1,40 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김대희\Desktop\정리-LATEX 2020.12.19 토\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansy6\OneDrive\바탕 화면\정리-LATEX 2020.12.24 목\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D99794A-20F5-48C1-B9F5-64FD52EEA503}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC2B1FB-089E-4B8C-9494-66921695629E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="포교사-1" sheetId="3" r:id="rId3"/>
-    <sheet name="법은회" sheetId="4" r:id="rId4"/>
-    <sheet name="경덕회" sheetId="5" r:id="rId5"/>
-    <sheet name="기타" sheetId="6" r:id="rId6"/>
+    <sheet name="개정이력" sheetId="7" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId3"/>
+    <sheet name="포교사-1" sheetId="3" r:id="rId4"/>
+    <sheet name="법은회" sheetId="4" r:id="rId5"/>
+    <sheet name="경덕회" sheetId="5" r:id="rId6"/>
+    <sheet name="기타" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">경덕회!$B$2:$I$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">기타!$B$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">법은회!$B$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'포교사-1'!$B$2:$I$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$AE$56</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Sheet1 (2)'!$A$1:$G$164</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">경덕회!$B$1:$I$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">기타!$B$1:$I$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">법은회!$B$1:$I$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'포교사-1'!$B$1:$I$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">경덕회!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">기타!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">법은회!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'포교사-1'!$1:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">경덕회!$B$2:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">기타!$B$2:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">법은회!$B$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'포교사-1'!$B$2:$I$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Sheet1!$A$1:$AE$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Sheet1 (2)'!$A$1:$G$164</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">경덕회!$B$1:$I$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">기타!$B$1:$I$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">법은회!$B$1:$I$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'포교사-1'!$B$1:$I$28</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">경덕회!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">기타!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">법은회!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'포교사-1'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="241">
   <si>
     <t>보운</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -377,46 +378,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>배소남</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김근영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>880327-
-1095312</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4809-1515</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경남 울산시 중구 우정동 500-10
-유성프라자 7층</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>변미자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>560117-
-2531717</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4552-9893</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부산 영도구 향토길 14번길
-12동 5호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>안해영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -457,36 +418,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이정수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이홍준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>871219-
-1824415</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2500-0732</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부산 연제구 거제3동
-현대@104-608</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정남선</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>징은영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>801213-
 2101414</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -496,11 +427,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>경기 안양시 안양전서로 177
-레미안메가트리아 116-2404</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>최미경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -622,11 +548,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>부산 사하구 하신번영로400
-SK@114-902호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>440102-
 2105416</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -645,11 +566,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>동래구 성가북로95번길31
-A동202호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>장은영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -714,10 +630,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>강명옥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>630509-
 2916715</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -768,24 +680,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>조석훈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>640915-
-1100918</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2816-1529</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부산시 사하구 다대로 301
-장림현대@11-605호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>김명애</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1163,6 +1057,53 @@
   <si>
     <t>부산시 북구 백양대로1016번길10
 삼정그린코아@102-2004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연말 정산건 조정 카톡 내용 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김형덕
+박영애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차홍선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>630508-
+2113811</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9802-2906</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사상구 백양대로 906
+우성@101동1401호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강영옥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1170,14 +1111,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="0000.0000"/>
     <numFmt numFmtId="177" formatCode="000000\-0000000"/>
     <numFmt numFmtId="178" formatCode="0000\-0000"/>
     <numFmt numFmtId="179" formatCode="00000"/>
     <numFmt numFmtId="180" formatCode="#,##0_ "/>
+    <numFmt numFmtId="181" formatCode="aaa"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1231,8 +1173,19 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1254,12 +1207,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1404,7 +1351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1472,18 +1419,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2397,39 +2348,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CB26F31-3C41-4C8D-B9B0-9BE29F08E14C}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="37">
+        <v>44190</v>
+      </c>
+      <c r="C2" s="36">
+        <f>B2</f>
+        <v>44190</v>
+      </c>
+      <c r="D2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B6:AD59"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.59765625" customWidth="1"/>
-    <col min="2" max="2" width="0.59765625" customWidth="1"/>
-    <col min="4" max="4" width="0.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.59765625" customWidth="1"/>
-    <col min="7" max="7" width="1.59765625" customWidth="1"/>
-    <col min="8" max="8" width="0.59765625" customWidth="1"/>
-    <col min="10" max="10" width="0.59765625" customWidth="1"/>
-    <col min="11" max="11" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="0.59765625" customWidth="1"/>
-    <col min="13" max="13" width="1.59765625" customWidth="1"/>
-    <col min="14" max="14" width="0.59765625" customWidth="1"/>
-    <col min="16" max="16" width="0.59765625" customWidth="1"/>
-    <col min="17" max="17" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="0.59765625" customWidth="1"/>
-    <col min="19" max="19" width="1.59765625" customWidth="1"/>
-    <col min="20" max="20" width="0.59765625" customWidth="1"/>
-    <col min="22" max="22" width="0.59765625" customWidth="1"/>
-    <col min="23" max="23" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="0.59765625" customWidth="1"/>
-    <col min="25" max="25" width="1.59765625" customWidth="1"/>
-    <col min="26" max="26" width="0.59765625" customWidth="1"/>
-    <col min="28" max="28" width="0.59765625" customWidth="1"/>
-    <col min="29" max="29" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="0.59765625" customWidth="1"/>
-    <col min="31" max="31" width="1.59765625" customWidth="1"/>
+    <col min="1" max="1" width="1.625" customWidth="1"/>
+    <col min="2" max="2" width="0.625" customWidth="1"/>
+    <col min="4" max="4" width="0.625" customWidth="1"/>
+    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.625" customWidth="1"/>
+    <col min="7" max="7" width="1.625" customWidth="1"/>
+    <col min="8" max="8" width="0.625" customWidth="1"/>
+    <col min="10" max="10" width="0.625" customWidth="1"/>
+    <col min="11" max="11" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="0.625" customWidth="1"/>
+    <col min="13" max="13" width="1.625" customWidth="1"/>
+    <col min="14" max="14" width="0.625" customWidth="1"/>
+    <col min="16" max="16" width="0.625" customWidth="1"/>
+    <col min="17" max="17" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="0.625" customWidth="1"/>
+    <col min="19" max="19" width="1.625" customWidth="1"/>
+    <col min="20" max="20" width="0.625" customWidth="1"/>
+    <col min="22" max="22" width="0.625" customWidth="1"/>
+    <col min="23" max="23" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="0.625" customWidth="1"/>
+    <col min="25" max="25" width="1.625" customWidth="1"/>
+    <col min="26" max="26" width="0.625" customWidth="1"/>
+    <col min="28" max="28" width="0.625" customWidth="1"/>
+    <col min="29" max="29" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="0.625" customWidth="1"/>
+    <col min="31" max="31" width="1.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -2456,7 +2449,7 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
     </row>
-    <row r="7" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -2483,7 +2476,7 @@
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
     </row>
-    <row r="8" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -2500,47 +2493,47 @@
       <c r="AC8" s="2"/>
       <c r="AD8" s="10"/>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
       <c r="F9" s="11"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
       <c r="R9" s="11"/>
       <c r="Z9" s="4"/>
-      <c r="AA9" s="41" t="s">
+      <c r="AA9" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="41"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
       <c r="AD9" s="11"/>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
       <c r="F10" s="11"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="45"/>
       <c r="R10" s="11"/>
       <c r="Z10" s="4"/>
-      <c r="AA10" s="41"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="41"/>
+      <c r="AA10" s="45"/>
+      <c r="AB10" s="45"/>
+      <c r="AC10" s="45"/>
       <c r="AD10" s="11"/>
     </row>
-    <row r="11" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="13"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -2557,8 +2550,8 @@
       <c r="AC11" s="14"/>
       <c r="AD11" s="12"/>
     </row>
-    <row r="12" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="13" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2575,7 +2568,7 @@
       <c r="AC13" s="2"/>
       <c r="AD13" s="3"/>
     </row>
-    <row r="14" spans="2:30" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:30" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B14" s="4"/>
       <c r="C14" s="16" t="s">
         <v>32</v>
@@ -2604,7 +2597,7 @@
       </c>
       <c r="AD14" s="6"/>
     </row>
-    <row r="15" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2621,7 +2614,7 @@
       <c r="AC15" s="5"/>
       <c r="AD15" s="6"/>
     </row>
-    <row r="16" spans="2:30" ht="18" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:30" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B16" s="4"/>
       <c r="C16" s="17">
         <v>15</v>
@@ -2650,7 +2643,7 @@
       </c>
       <c r="AD16" s="6"/>
     </row>
-    <row r="17" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -2667,8 +2660,8 @@
       <c r="AC17" s="8"/>
       <c r="AD17" s="9"/>
     </row>
-    <row r="18" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -2680,7 +2673,7 @@
       <c r="AC19" s="2"/>
       <c r="AD19" s="3"/>
     </row>
-    <row r="20" spans="2:30" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:30" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B20" s="4"/>
       <c r="C20" s="16" t="s">
         <v>34</v>
@@ -2700,7 +2693,7 @@
       </c>
       <c r="AD20" s="6"/>
     </row>
-    <row r="21" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -2712,7 +2705,7 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="6"/>
     </row>
-    <row r="22" spans="2:30" ht="18" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:30" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B22" s="4"/>
       <c r="C22" s="17">
         <v>18</v>
@@ -2732,7 +2725,7 @@
       </c>
       <c r="AD22" s="6"/>
     </row>
-    <row r="23" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2744,7 +2737,7 @@
       <c r="AC23" s="8"/>
       <c r="AD23" s="9"/>
     </row>
-    <row r="24" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -2771,7 +2764,7 @@
       <c r="AC24" s="5"/>
       <c r="AD24" s="5"/>
     </row>
-    <row r="25" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -2798,7 +2791,7 @@
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
     </row>
-    <row r="26" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -2825,7 +2818,7 @@
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
     </row>
-    <row r="27" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -2852,7 +2845,7 @@
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
     </row>
-    <row r="28" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="1"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -2879,71 +2872,71 @@
       <c r="AC28" s="2"/>
       <c r="AD28" s="10"/>
     </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
       <c r="F29" s="11"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
       <c r="L29" s="11"/>
       <c r="N29" s="4"/>
-      <c r="O29" s="41" t="s">
+      <c r="O29" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
       <c r="R29" s="11"/>
       <c r="T29" s="4"/>
-      <c r="U29" s="41" t="s">
+      <c r="U29" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="V29" s="41"/>
-      <c r="W29" s="41"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="45"/>
       <c r="X29" s="11"/>
       <c r="Z29" s="4"/>
-      <c r="AA29" s="41" t="s">
+      <c r="AA29" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="AB29" s="41"/>
-      <c r="AC29" s="41"/>
+      <c r="AB29" s="45"/>
+      <c r="AC29" s="45"/>
       <c r="AD29" s="11"/>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B30" s="4"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
       <c r="F30" s="11"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
       <c r="L30" s="11"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="41"/>
-      <c r="Q30" s="41"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
       <c r="R30" s="11"/>
       <c r="T30" s="4"/>
-      <c r="U30" s="41"/>
-      <c r="V30" s="41"/>
-      <c r="W30" s="41"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
       <c r="X30" s="11"/>
       <c r="Z30" s="4"/>
-      <c r="AA30" s="41"/>
-      <c r="AB30" s="41"/>
-      <c r="AC30" s="41"/>
+      <c r="AA30" s="45"/>
+      <c r="AB30" s="45"/>
+      <c r="AC30" s="45"/>
       <c r="AD30" s="11"/>
     </row>
-    <row r="31" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="13"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -2970,8 +2963,8 @@
       <c r="AC31" s="14"/>
       <c r="AD31" s="12"/>
     </row>
-    <row r="32" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -2998,7 +2991,7 @@
       <c r="AC33" s="2"/>
       <c r="AD33" s="3"/>
     </row>
-    <row r="34" spans="2:30" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:30" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B34" s="4"/>
       <c r="C34" s="16" t="s">
         <v>2</v>
@@ -3045,7 +3038,7 @@
       </c>
       <c r="AD34" s="6"/>
     </row>
-    <row r="35" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3072,7 +3065,7 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="6"/>
     </row>
-    <row r="36" spans="2:30" ht="18" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:30" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B36" s="4"/>
       <c r="C36" s="17">
         <v>18</v>
@@ -3119,7 +3112,7 @@
       </c>
       <c r="AD36" s="6"/>
     </row>
-    <row r="37" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -3146,8 +3139,8 @@
       <c r="AC37" s="8"/>
       <c r="AD37" s="9"/>
     </row>
-    <row r="38" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -3174,7 +3167,7 @@
       <c r="AC39" s="2"/>
       <c r="AD39" s="3"/>
     </row>
-    <row r="40" spans="2:30" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="2:30" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B40" s="4"/>
       <c r="C40" s="16" t="s">
         <v>10</v>
@@ -3221,7 +3214,7 @@
       </c>
       <c r="AD40" s="6"/>
     </row>
-    <row r="41" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -3248,7 +3241,7 @@
       <c r="AC41" s="5"/>
       <c r="AD41" s="6"/>
     </row>
-    <row r="42" spans="2:30" ht="18" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:30" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B42" s="4"/>
       <c r="C42" s="17">
         <v>23</v>
@@ -3295,7 +3288,7 @@
       </c>
       <c r="AD42" s="6"/>
     </row>
-    <row r="43" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="7"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -3322,8 +3315,8 @@
       <c r="AC43" s="8"/>
       <c r="AD43" s="9"/>
     </row>
-    <row r="44" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H45" s="1"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -3340,7 +3333,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="3"/>
     </row>
-    <row r="46" spans="2:30" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="2:30" ht="19.5" x14ac:dyDescent="0.45">
       <c r="H46" s="4"/>
       <c r="I46" s="16" t="s">
         <v>8</v>
@@ -3369,7 +3362,7 @@
       </c>
       <c r="X46" s="6"/>
     </row>
-    <row r="47" spans="2:30" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:30" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H47" s="4"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -3386,7 +3379,7 @@
       <c r="W47" s="5"/>
       <c r="X47" s="6"/>
     </row>
-    <row r="48" spans="2:30" ht="18" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:30" ht="18.75" x14ac:dyDescent="0.4">
       <c r="H48" s="4"/>
       <c r="I48" s="17">
         <v>23</v>
@@ -3415,7 +3408,7 @@
       </c>
       <c r="X48" s="6"/>
     </row>
-    <row r="49" spans="3:29" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:29" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H49" s="7"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
@@ -3432,8 +3425,8 @@
       <c r="W49" s="8"/>
       <c r="X49" s="9"/>
     </row>
-    <row r="50" spans="3:29" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" spans="3:29" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:29" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="3:29" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N51" s="1"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -3445,7 +3438,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="3:29" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="3:29" ht="19.5" x14ac:dyDescent="0.45">
       <c r="N52" s="4"/>
       <c r="O52" s="16" t="s">
         <v>24</v>
@@ -3465,7 +3458,7 @@
       </c>
       <c r="X52" s="6"/>
     </row>
-    <row r="53" spans="3:29" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:29" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N53" s="4"/>
       <c r="O53" s="5"/>
       <c r="P53" s="5"/>
@@ -3477,7 +3470,7 @@
       <c r="W53" s="5"/>
       <c r="X53" s="6"/>
     </row>
-    <row r="54" spans="3:29" ht="18" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:29" ht="18.75" x14ac:dyDescent="0.4">
       <c r="N54" s="4"/>
       <c r="O54" s="17">
         <v>25</v>
@@ -3497,7 +3490,7 @@
       </c>
       <c r="X54" s="6"/>
     </row>
-    <row r="55" spans="3:29" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:29" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N55" s="7"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
@@ -3509,17 +3502,17 @@
       <c r="W55" s="8"/>
       <c r="X55" s="9"/>
     </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:29" x14ac:dyDescent="0.3">
       <c r="AC56" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>41</v>
       </c>
@@ -3546,317 +3539,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157748CB-3DCC-44CE-BFA5-9B56B1B73E37}">
   <dimension ref="B2:F167"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.59765625" customWidth="1"/>
-    <col min="2" max="2" width="0.59765625" customWidth="1"/>
-    <col min="4" max="4" width="0.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="0.59765625" customWidth="1"/>
-    <col min="7" max="7" width="1.59765625" customWidth="1"/>
+    <col min="1" max="1" width="1.625" customWidth="1"/>
+    <col min="2" max="2" width="0.625" customWidth="1"/>
+    <col min="4" max="4" width="0.625" customWidth="1"/>
+    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="0.625" customWidth="1"/>
+    <col min="7" max="7" width="1.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="10"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
       <c r="F3" s="11"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="11"/>
     </row>
-    <row r="5" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
       <c r="F8" s="11"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
       <c r="F9" s="11"/>
     </row>
-    <row r="10" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="13"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="10"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="11"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="10"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
       <c r="F18" s="11"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
       <c r="F19" s="11"/>
     </row>
-    <row r="20" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="13"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="1"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="10"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="4"/>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="11"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="4"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="11"/>
     </row>
-    <row r="25" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="13"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="1"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="10"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4"/>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
       <c r="F28" s="11"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
       <c r="F29" s="11"/>
     </row>
-    <row r="30" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="13"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="1"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="10"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4"/>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
       <c r="F34" s="11"/>
     </row>
-    <row r="35" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="13"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="10"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="4"/>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
       <c r="F38" s="11"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="4"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
+      <c r="C39" s="45"/>
+      <c r="D39" s="45"/>
+      <c r="E39" s="45"/>
       <c r="F39" s="11"/>
     </row>
-    <row r="40" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="13"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B43" s="4"/>
       <c r="C43" s="16" t="s">
         <v>32</v>
@@ -3867,14 +3860,14 @@
       </c>
       <c r="F43" s="6"/>
     </row>
-    <row r="44" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="6"/>
     </row>
-    <row r="45" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B45" s="4"/>
       <c r="C45" s="17">
         <v>15</v>
@@ -3885,22 +3878,22 @@
       </c>
       <c r="F45" s="6"/>
     </row>
-    <row r="46" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="1"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B49" s="4"/>
       <c r="C49" s="16" t="s">
         <v>36</v>
@@ -3911,14 +3904,14 @@
       </c>
       <c r="F49" s="6"/>
     </row>
-    <row r="50" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B51" s="4"/>
       <c r="C51" s="17">
         <v>15</v>
@@ -3929,29 +3922,29 @@
       </c>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="7"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="9"/>
     </row>
-    <row r="53" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
     </row>
-    <row r="54" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="1"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B56" s="4"/>
       <c r="C56" s="16" t="s">
         <v>38</v>
@@ -3962,14 +3955,14 @@
       </c>
       <c r="F56" s="6"/>
     </row>
-    <row r="57" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B58" s="4"/>
       <c r="C58" s="17">
         <v>16</v>
@@ -3980,28 +3973,28 @@
       </c>
       <c r="F58" s="6"/>
     </row>
-    <row r="59" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="7"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="9"/>
     </row>
-    <row r="60" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
     </row>
-    <row r="61" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="1"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B62" s="4"/>
       <c r="C62" s="16" t="s">
         <v>13</v>
@@ -4012,14 +4005,14 @@
       </c>
       <c r="F62" s="6"/>
     </row>
-    <row r="63" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="6"/>
     </row>
-    <row r="64" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B64" s="4"/>
       <c r="C64" s="17">
         <v>17</v>
@@ -4030,22 +4023,22 @@
       </c>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="7"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="9"/>
     </row>
-    <row r="66" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="67" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B68" s="4"/>
       <c r="C68" s="16" t="s">
         <v>15</v>
@@ -4056,14 +4049,14 @@
       </c>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B70" s="4"/>
       <c r="C70" s="17">
         <v>17</v>
@@ -4074,22 +4067,22 @@
       </c>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
       <c r="F71" s="9"/>
     </row>
-    <row r="72" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="73" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="1"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B74" s="4"/>
       <c r="C74" s="16" t="s">
         <v>20</v>
@@ -4100,14 +4093,14 @@
       </c>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="4"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B76" s="4"/>
       <c r="C76" s="17">
         <v>18</v>
@@ -4118,22 +4111,22 @@
       </c>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="9"/>
     </row>
-    <row r="78" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="79" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="1"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B80" s="4"/>
       <c r="C80" s="16" t="s">
         <v>2</v>
@@ -4144,14 +4137,14 @@
       </c>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="4"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B82" s="4"/>
       <c r="C82" s="17">
         <v>18</v>
@@ -4162,22 +4155,22 @@
       </c>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="7"/>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
       <c r="E83" s="8"/>
       <c r="F83" s="9"/>
     </row>
-    <row r="84" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="85" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="1"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B86" s="4"/>
       <c r="C86" s="16" t="s">
         <v>34</v>
@@ -4188,14 +4181,14 @@
       </c>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B88" s="4"/>
       <c r="C88" s="17">
         <v>18</v>
@@ -4206,22 +4199,22 @@
       </c>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8"/>
       <c r="F89" s="9"/>
     </row>
-    <row r="90" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="91" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="1"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B92" s="4"/>
       <c r="C92" s="16" t="s">
         <v>27</v>
@@ -4232,14 +4225,14 @@
       </c>
       <c r="F92" s="6"/>
     </row>
-    <row r="93" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="4"/>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B94" s="4"/>
       <c r="C94" s="17">
         <v>18</v>
@@ -4250,22 +4243,22 @@
       </c>
       <c r="F94" s="6"/>
     </row>
-    <row r="95" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="7"/>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
       <c r="E95" s="8"/>
       <c r="F95" s="9"/>
     </row>
-    <row r="96" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="97" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="1"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B98" s="4"/>
       <c r="C98" s="16" t="s">
         <v>17</v>
@@ -4276,14 +4269,14 @@
       </c>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="4"/>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
       <c r="E99" s="5"/>
       <c r="F99" s="6"/>
     </row>
-    <row r="100" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B100" s="4"/>
       <c r="C100" s="17">
         <v>19</v>
@@ -4294,28 +4287,28 @@
       </c>
       <c r="F100" s="6"/>
     </row>
-    <row r="101" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="7"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
       <c r="E101" s="8"/>
       <c r="F101" s="9"/>
     </row>
-    <row r="102" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
     </row>
-    <row r="103" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="1"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B104" s="4"/>
       <c r="C104" s="16" t="s">
         <v>29</v>
@@ -4326,14 +4319,14 @@
       </c>
       <c r="F104" s="6"/>
     </row>
-    <row r="105" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="4"/>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="6"/>
     </row>
-    <row r="106" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B106" s="4"/>
       <c r="C106" s="17">
         <v>20</v>
@@ -4344,28 +4337,28 @@
       </c>
       <c r="F106" s="6"/>
     </row>
-    <row r="107" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="7"/>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
       <c r="E107" s="8"/>
       <c r="F107" s="9"/>
     </row>
-    <row r="108" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
     </row>
-    <row r="109" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="1"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B110" s="4"/>
       <c r="C110" s="16" t="s">
         <v>4</v>
@@ -4376,14 +4369,14 @@
       </c>
       <c r="F110" s="6"/>
     </row>
-    <row r="111" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="4"/>
       <c r="C111" s="5"/>
       <c r="D111" s="5"/>
       <c r="E111" s="5"/>
       <c r="F111" s="6"/>
     </row>
-    <row r="112" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B112" s="4"/>
       <c r="C112" s="17">
         <v>21</v>
@@ -4394,22 +4387,22 @@
       </c>
       <c r="F112" s="6"/>
     </row>
-    <row r="113" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="7"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8"/>
       <c r="F113" s="9"/>
     </row>
-    <row r="114" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="115" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="1"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B116" s="4"/>
       <c r="C116" s="16" t="s">
         <v>0</v>
@@ -4420,14 +4413,14 @@
       </c>
       <c r="F116" s="6"/>
     </row>
-    <row r="117" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="4"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="6"/>
     </row>
-    <row r="118" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B118" s="4"/>
       <c r="C118" s="17">
         <v>21</v>
@@ -4438,29 +4431,29 @@
       </c>
       <c r="F118" s="6"/>
     </row>
-    <row r="119" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
       <c r="F119" s="9"/>
     </row>
-    <row r="120" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
     </row>
-    <row r="121" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="122" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B122" s="1"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B123" s="4"/>
       <c r="C123" s="16" t="s">
         <v>0</v>
@@ -4471,14 +4464,14 @@
       </c>
       <c r="F123" s="6"/>
     </row>
-    <row r="124" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="4"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="6"/>
     </row>
-    <row r="125" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B125" s="4"/>
       <c r="C125" s="17">
         <v>21</v>
@@ -4489,28 +4482,28 @@
       </c>
       <c r="F125" s="6"/>
     </row>
-    <row r="126" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="9"/>
     </row>
-    <row r="127" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
     </row>
-    <row r="128" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="1"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B129" s="4"/>
       <c r="C129" s="16" t="s">
         <v>6</v>
@@ -4521,14 +4514,14 @@
       </c>
       <c r="F129" s="6"/>
     </row>
-    <row r="130" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B130" s="4"/>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="6"/>
     </row>
-    <row r="131" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B131" s="4"/>
       <c r="C131" s="17">
         <v>22</v>
@@ -4539,22 +4532,22 @@
       </c>
       <c r="F131" s="6"/>
     </row>
-    <row r="132" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B132" s="7"/>
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="9"/>
     </row>
-    <row r="133" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="134" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B134" s="1"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B135" s="4"/>
       <c r="C135" s="16" t="s">
         <v>6</v>
@@ -4565,14 +4558,14 @@
       </c>
       <c r="F135" s="6"/>
     </row>
-    <row r="136" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B136" s="4"/>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="6"/>
     </row>
-    <row r="137" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B137" s="4"/>
       <c r="C137" s="17">
         <v>22</v>
@@ -4583,22 +4576,22 @@
       </c>
       <c r="F137" s="6"/>
     </row>
-    <row r="138" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B138" s="7"/>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
       <c r="E138" s="8"/>
       <c r="F138" s="9"/>
     </row>
-    <row r="139" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="140" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B140" s="1"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B141" s="4"/>
       <c r="C141" s="16" t="s">
         <v>8</v>
@@ -4609,14 +4602,14 @@
       </c>
       <c r="F141" s="6"/>
     </row>
-    <row r="142" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B142" s="4"/>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
       <c r="E142" s="5"/>
       <c r="F142" s="6"/>
     </row>
-    <row r="143" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B143" s="4"/>
       <c r="C143" s="17">
         <v>23</v>
@@ -4627,22 +4620,22 @@
       </c>
       <c r="F143" s="6"/>
     </row>
-    <row r="144" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B144" s="7"/>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8"/>
       <c r="F144" s="9"/>
     </row>
-    <row r="145" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="146" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B146" s="1"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B147" s="4"/>
       <c r="C147" s="16" t="s">
         <v>10</v>
@@ -4653,14 +4646,14 @@
       </c>
       <c r="F147" s="6"/>
     </row>
-    <row r="148" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B148" s="4"/>
       <c r="C148" s="5"/>
       <c r="D148" s="5"/>
       <c r="E148" s="5"/>
       <c r="F148" s="6"/>
     </row>
-    <row r="149" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B149" s="4"/>
       <c r="C149" s="17">
         <v>23</v>
@@ -4671,22 +4664,22 @@
       </c>
       <c r="F149" s="6"/>
     </row>
-    <row r="150" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B150" s="7"/>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
       <c r="E150" s="8"/>
       <c r="F150" s="9"/>
     </row>
-    <row r="151" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="152" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B152" s="1"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B153" s="4"/>
       <c r="C153" s="16" t="s">
         <v>22</v>
@@ -4697,14 +4690,14 @@
       </c>
       <c r="F153" s="6"/>
     </row>
-    <row r="154" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B154" s="4"/>
       <c r="C154" s="5"/>
       <c r="D154" s="5"/>
       <c r="E154" s="5"/>
       <c r="F154" s="6"/>
     </row>
-    <row r="155" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B155" s="4"/>
       <c r="C155" s="17">
         <v>24</v>
@@ -4715,22 +4708,22 @@
       </c>
       <c r="F155" s="6"/>
     </row>
-    <row r="156" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B156" s="7"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
       <c r="E156" s="8"/>
       <c r="F156" s="9"/>
     </row>
-    <row r="157" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="158" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B158" s="1"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" spans="2:6" ht="19.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="2:6" ht="19.5" x14ac:dyDescent="0.45">
       <c r="B159" s="4"/>
       <c r="C159" s="16" t="s">
         <v>24</v>
@@ -4741,14 +4734,14 @@
       </c>
       <c r="F159" s="6"/>
     </row>
-    <row r="160" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B160" s="4"/>
       <c r="C160" s="5"/>
       <c r="D160" s="5"/>
       <c r="E160" s="5"/>
       <c r="F160" s="6"/>
     </row>
-    <row r="161" spans="2:6" ht="18" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="B161" s="4"/>
       <c r="C161" s="17">
         <v>25</v>
@@ -4759,26 +4752,26 @@
       </c>
       <c r="F161" s="6"/>
     </row>
-    <row r="162" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B162" s="7"/>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
       <c r="E162" s="8"/>
       <c r="F162" s="9"/>
     </row>
-    <row r="163" spans="2:6" ht="3.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="2:6" ht="3.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
       <c r="D163" s="5"/>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
         <v>41</v>
       </c>
@@ -4804,25 +4797,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7AE0259-8F09-4183-9537-9A7D3DCA8641}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.69921875" customWidth="1"/>
-    <col min="3" max="4" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="8" max="8" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="3.75" customWidth="1"/>
+    <col min="3" max="4" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="29" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -4830,9 +4824,9 @@
       <c r="H1" s="32"/>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>50</v>
@@ -4859,7 +4853,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="49.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -4875,8 +4869,8 @@
       <c r="F3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="40">
-        <v>510000</v>
+      <c r="G3" s="35">
+        <v>550000</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>60</v>
@@ -4885,9 +4879,9 @@
         <v>48422</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23">
-        <f t="shared" ref="B4:B32" si="0">B3+1</f>
+        <f>B3+1</f>
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
@@ -4902,7 +4896,7 @@
       <c r="F4" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="35">
         <v>810000</v>
       </c>
       <c r="H4" s="26" t="s">
@@ -4912,9 +4906,9 @@
         <v>13595</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="23">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B5:B25" si="0">B4+1</f>
         <v>3</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -4929,7 +4923,7 @@
       <c r="F5" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="35">
         <v>820000</v>
       </c>
       <c r="H5" s="26" t="s">
@@ -4939,7 +4933,7 @@
         <v>47848</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -4948,23 +4942,23 @@
         <v>35</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="40">
-        <v>750000</v>
+        <v>87</v>
+      </c>
+      <c r="G6" s="35">
+        <v>700000</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="I6" s="23"/>
     </row>
-    <row r="7" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -4973,7 +4967,7 @@
         <v>35</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>65</v>
@@ -4981,8 +4975,8 @@
       <c r="F7" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="40">
-        <v>510000</v>
+      <c r="G7" s="35">
+        <v>550000</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>67</v>
@@ -4991,7 +4985,7 @@
         <v>47848</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -5008,7 +5002,7 @@
       <c r="F8" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="35">
         <v>800000</v>
       </c>
       <c r="H8" s="26" t="s">
@@ -5018,7 +5012,7 @@
         <v>49078</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="23">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -5027,23 +5021,23 @@
         <v>30</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="40">
+        <v>116</v>
+      </c>
+      <c r="G9" s="35">
         <v>300000</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -5060,8 +5054,8 @@
       <c r="F10" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="40">
-        <v>800000</v>
+      <c r="G10" s="35">
+        <v>810000</v>
       </c>
       <c r="H10" s="26" t="s">
         <v>76</v>
@@ -5070,657 +5064,476 @@
         <v>47206</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>9</v>
+      <c r="C11" s="26" t="s">
+        <v>235</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F11" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="G11" s="40">
-        <v>510000</v>
+        <v>107</v>
+      </c>
+      <c r="G11" s="35">
+        <v>1100000</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I11" s="23">
         <v>15871</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="G12" s="40">
-        <v>510000</v>
+        <v>95</v>
+      </c>
+      <c r="G12" s="35">
+        <v>550000</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" s="23">
-        <v>15871</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+      <c r="I12" s="27">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="23">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="40">
-        <v>510000</v>
+        <v>80</v>
+      </c>
+      <c r="G13" s="35">
+        <v>500000</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="27">
-        <v>4974</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+      <c r="I13" s="23">
+        <v>49302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="I14" s="35">
-        <v>44542</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="35">
+        <v>700000</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="23">
+        <v>46726</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="23">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H15" s="38" t="s">
+      <c r="G15" s="35">
+        <v>820000</v>
+      </c>
+      <c r="H15" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="35">
-        <v>49082</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="I15" s="23">
+        <v>49302</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="23">
-        <f>B13+1</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="40">
-        <v>500000</v>
+        <v>111</v>
+      </c>
+      <c r="G16" s="35">
+        <v>700000</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="I16" s="23">
-        <v>49302</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="23">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F17" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="40">
-        <v>700000</v>
+        <v>203</v>
+      </c>
+      <c r="G17" s="35">
+        <v>500000</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I17" s="23">
-        <v>46726</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>14038</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="23">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="40">
-        <v>820000</v>
+        <v>204</v>
+      </c>
+      <c r="G18" s="35">
+        <v>800000</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="I18" s="23">
-        <v>49302</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="23">
+        <v>47263</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" s="39" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="40">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H19" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="35">
-        <v>49302</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="23">
+        <v>17</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="43">
+        <v>500000</v>
+      </c>
+      <c r="H19" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="40">
+        <v>50959</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" s="39" customFormat="1" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="40">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="G20" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="35">
-        <v>47537</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="43">
+        <v>550000</v>
+      </c>
+      <c r="H20" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="40">
+        <v>46637</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="23">
-        <f>B18+1</f>
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>126</v>
+        <v>236</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>127</v>
+        <v>237</v>
       </c>
       <c r="F21" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" s="40">
-        <v>7000000</v>
+        <v>238</v>
+      </c>
+      <c r="G21" s="35">
+        <v>500000</v>
       </c>
       <c r="H21" s="26" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="I21" s="23">
-        <v>46296</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+        <v>46928</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="23">
         <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="35">
+        <v>700000</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" s="23">
+        <v>49511</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="23">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G22" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H22" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="I22" s="35">
-        <v>14038</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="23">
-        <f>B21+1</f>
+      <c r="D23" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>140</v>
-      </c>
       <c r="E23" s="24" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="G23" s="40">
-        <v>510000</v>
+        <v>114</v>
+      </c>
+      <c r="G23" s="35">
+        <v>550000</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="I23" s="23">
-        <v>14038</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>47206</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="23">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>39</v>
+        <v>240</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>143</v>
+        <v>240</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F24" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="G24" s="40">
-        <v>510000</v>
+        <v>134</v>
+      </c>
+      <c r="G24" s="35">
+        <v>500000</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I24" s="23">
-        <v>47263</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50626</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="23">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="40">
+        <v>222</v>
+      </c>
+      <c r="G25" s="35">
         <v>500000</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="I25" s="23">
-        <v>50959</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" s="39" customFormat="1" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+        <v>48798</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="23">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="35" t="s">
+        <f t="shared" ref="B26:B27" si="1">B25+1</f>
+        <v>24</v>
+      </c>
+      <c r="C26" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H26" s="38" t="s">
+      <c r="D26" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="I26" s="35"/>
-    </row>
-    <row r="27" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="F26" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G26" s="23"/>
+      <c r="H26" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="I26" s="23">
+        <v>63257</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="49.9" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="23">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>39</v>
+        <v>140</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="F27" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="G27" s="40">
-        <v>510000</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G27" s="23"/>
       <c r="H27" s="26" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="I27" s="23">
-        <v>49511</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="23">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="G28" s="40">
-        <v>520000</v>
-      </c>
-      <c r="H28" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="I28" s="23">
-        <v>46637</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="23">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" s="40">
-        <v>700000</v>
-      </c>
-      <c r="H29" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="I29" s="23">
-        <v>49511</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="23">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="G30" s="40">
-        <v>550000</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="23">
-        <v>47206</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="23">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="F31" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G31" s="40">
-        <v>550000</v>
-      </c>
-      <c r="H31" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="I31" s="23">
-        <v>50626</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="23">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="G32" s="40">
-        <v>500000</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="I32" s="23">
-        <v>48798</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="23">
-        <f t="shared" ref="B33:B34" si="1">B32+1</f>
-        <v>26</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="23">
-        <v>63257</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="23">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="I34" s="23">
         <v>48766</v>
       </c>
     </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G28" s="38">
+        <f>SUBTOTAL(109,G3:G25)</f>
+        <v>14810000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:I32" xr:uid="{6092F43B-7E66-43C6-B6C5-0EA0C354B4C3}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:I32">
-      <sortCondition ref="C2:C32"/>
+  <autoFilter ref="B2:I25" xr:uid="{6092F43B-7E66-43C6-B6C5-0EA0C354B4C3}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:I25">
+      <sortCondition ref="C2:C25"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="1.5748031496062993" bottom="0.78740157480314965" header="0.78740157480314965" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L
 &amp;"HY견고딕,보통"&amp;18【 포교사-1 】&amp;C&amp;"HY견고딕,보통"&amp;18 2020년 청파팀 연말 정산</oddHeader>
@@ -5728,25 +5541,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1E5A23-ED8C-49AD-BBC2-9184AD833D91}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.69921875" customWidth="1"/>
-    <col min="3" max="4" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="8" max="8" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="3.75" customWidth="1"/>
+    <col min="3" max="4" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="29" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -5754,15 +5568,15 @@
       <c r="H1" s="32"/>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>50</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>52</v>
@@ -5783,423 +5597,429 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="49.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B3" s="23">
         <v>1</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="E3" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>187</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="G3" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>211</v>
       </c>
       <c r="I3" s="23">
         <v>44062</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B4" s="23">
         <f>B3+1</f>
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="E4" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H4" s="26" t="s">
         <v>188</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="G4" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>212</v>
       </c>
       <c r="I4" s="23">
         <v>47605</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B5" s="23">
         <f t="shared" ref="B5:B14" si="0">B4+1</f>
         <v>3</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="E5" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>189</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>213</v>
       </c>
       <c r="I5" s="23">
         <v>46246</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B6" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="E6" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="G6" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>190</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>214</v>
       </c>
       <c r="I6" s="23">
         <v>47508</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E7" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>191</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="G7" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>215</v>
       </c>
       <c r="I7" s="23">
         <v>48405</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B8" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="E8" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>192</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="G8" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>216</v>
       </c>
       <c r="I8" s="23">
         <v>52039</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B9" s="23">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="E9" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>193</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="G9" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>217</v>
       </c>
       <c r="I9" s="23">
         <v>48724</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B10" s="23">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="E10" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="G10" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H10" s="26" t="s">
         <v>194</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="G10" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>218</v>
       </c>
       <c r="I10" s="23">
         <v>17336</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B11" s="23">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="E11" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>195</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>219</v>
       </c>
       <c r="I11" s="23">
         <v>47170</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B12" s="23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="E12" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G12" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>196</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="G12" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>220</v>
       </c>
       <c r="I12" s="23">
         <v>47817</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B13" s="23">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="E13" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H13" s="26" t="s">
         <v>197</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="G13" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>221</v>
       </c>
       <c r="I13" s="23">
         <v>47536</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B14" s="23">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="E14" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="35">
+        <v>350000</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>198</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="40">
-        <v>300000</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>222</v>
       </c>
       <c r="I14" s="23">
         <v>50547</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B15" s="23">
         <f>B14+1</f>
         <v>13</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="F15" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="G15" s="40">
-        <v>300000</v>
+        <v>138</v>
+      </c>
+      <c r="G15" s="35">
+        <v>350000</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="I15" s="23">
         <v>63257</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B16" s="23">
         <f>B15+1</f>
         <v>14</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="F16" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G16" s="40">
-        <v>300000</v>
+        <v>142</v>
+      </c>
+      <c r="G16" s="35">
+        <v>350000</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="I16" s="23">
         <v>48766</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G17" s="35">
+        <f>SUBTOTAL(109,G3:G16)</f>
+        <v>4900000</v>
       </c>
     </row>
   </sheetData>
@@ -6210,7 +6030,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="1.5748031496062993" bottom="0.78740157480314965" header="0.78740157480314965" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;L
 &amp;"HY견고딕,보통"&amp;18【 법은회 】&amp;C&amp;"HY견고딕,보통"&amp;18 2020년 청파팀 연말 정산 </oddHeader>
@@ -6218,25 +6038,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E967278A-4E84-46E7-89E2-75B2A847BBA4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.69921875" customWidth="1"/>
-    <col min="3" max="4" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="8" max="8" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="3.75" customWidth="1"/>
+    <col min="3" max="4" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="29" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -6244,9 +6064,9 @@
       <c r="H1" s="32"/>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>50</v>
@@ -6273,84 +6093,90 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="49.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8">
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="G3" s="40">
+        <v>214</v>
+      </c>
+      <c r="G3" s="35">
         <v>1020000</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="I3" s="8">
         <v>44751</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23">
         <f t="shared" ref="B4:B5" si="0">B3+1</f>
         <v>2</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="G4" s="40">
+        <v>215</v>
+      </c>
+      <c r="G4" s="35">
         <v>1020000</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="I4" s="23">
         <v>47822</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="G5" s="40">
+        <v>216</v>
+      </c>
+      <c r="G5" s="35">
         <v>1030000</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="I5" s="23">
         <v>48517</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G6" s="35">
+        <f>SUBTOTAL(109,G3:G5)</f>
+        <v>3070000</v>
       </c>
     </row>
   </sheetData>
@@ -6361,7 +6187,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="1.5748031496062993" bottom="0.78740157480314965" header="0.78740157480314965" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"HY견고딕,보통"&amp;18
 【 경덕회 】&amp;C&amp;"HY견고딕,보통"&amp;18 2020년 청파팀 연말 정산</oddHeader>
@@ -6369,25 +6195,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D88021-929C-4C73-A9E7-32C974001EEC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="3.69921875" customWidth="1"/>
-    <col min="3" max="4" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.69921875" customWidth="1"/>
-    <col min="8" max="8" width="37.69921875" customWidth="1"/>
+    <col min="2" max="2" width="3.75" customWidth="1"/>
+    <col min="3" max="4" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+    <col min="8" max="8" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="29" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E1" s="30"/>
       <c r="F1" s="31"/>
@@ -6395,9 +6221,9 @@
       <c r="H1" s="32"/>
       <c r="I1" s="29"/>
     </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>50</v>
@@ -6424,7 +6250,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="49.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B3" s="8">
         <v>1</v>
       </c>
@@ -6432,23 +6258,23 @@
         <v>30</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="20" t="s">
-        <v>249</v>
-      </c>
       <c r="F3" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="40"/>
+        <v>116</v>
+      </c>
+      <c r="G3" s="35"/>
       <c r="H3" s="22" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="I3" s="8">
         <v>49056</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="23">
         <f t="shared" ref="B4:B8" si="0">B3+1</f>
         <v>2</v>
@@ -6457,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="E4" s="24" t="s">
         <v>65</v>
@@ -6465,11 +6291,11 @@
       <c r="F4" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="40"/>
+      <c r="G4" s="35"/>
       <c r="H4" s="26"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -6478,23 +6304,23 @@
         <v>35</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="40"/>
+        <v>87</v>
+      </c>
+      <c r="G5" s="35"/>
       <c r="H5" s="26" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="I5" s="23">
         <v>14038</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="23">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -6503,21 +6329,21 @@
         <v>39</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="F6" s="25"/>
-      <c r="G6" s="40"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="26" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="I6" s="23">
         <v>47263</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -6526,21 +6352,21 @@
         <v>39</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="F7" s="25"/>
-      <c r="G7" s="40"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="26" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="I7" s="23">
         <v>48119</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="49.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="23">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -6549,17 +6375,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="40"/>
+        <v>128</v>
+      </c>
+      <c r="G8" s="35"/>
       <c r="H8" s="26" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="I8" s="23">
         <v>46637</v>
@@ -6573,7 +6399,7 @@
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="1.5748031496062993" bottom="0.78740157480314965" header="0.78740157480314965" footer="0.39370078740157483"/>
-  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;L
 &amp;"HY견고딕,보통"&amp;18【 기타 】 &amp;C&amp;"HY견고딕,보통"&amp;18 2020년 청파팀 연말 정산</oddHeader>
